--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488106_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488106_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7659</v>
+        <v>11.1081</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3691</v>
+        <v>6.2902</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3968</v>
+        <v>4.818</v>
       </c>
       <c r="G2" t="n">
         <v>8.0357</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7214</v>
+        <v>1.0636</v>
       </c>
       <c r="T2" t="n">
-        <v>0.694</v>
+        <v>0.615</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0274</v>
+        <v>0.4486</v>
       </c>
       <c r="V2" t="n">
         <v>1.8107</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6158</v>
+        <v>10.0439</v>
       </c>
       <c r="E3" t="n">
-        <v>3.631</v>
+        <v>5.8816</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9848</v>
+        <v>4.1623</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8661</v>
+        <v>4.3327</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6078</v>
+        <v>1.8588</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2583</v>
+        <v>2.4739</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5449</v>
+        <v>3.1491</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4395</v>
+        <v>1.3657</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1054</v>
+        <v>1.7834</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3212</v>
+        <v>1.1836</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1683</v>
+        <v>0.4931</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1529</v>
+        <v>0.6905</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3787</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2808</v>
+        <v>1.1076</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0772</v>
+        <v>0.7058</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2036</v>
+        <v>0.4018</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0813</v>
+        <v>3.0178</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="X3" t="n">
-        <v>1.0813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.455299999999999</v>
+        <v>9.593999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5738</v>
+        <v>4.4689</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8815</v>
+        <v>5.1252</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3327</v>
+        <v>5.8661</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8588</v>
+        <v>2.6078</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4739</v>
+        <v>3.2583</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1491</v>
+        <v>4.5449</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3657</v>
+        <v>1.4395</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7834</v>
+        <v>3.1054</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1836</v>
+        <v>1.3212</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4931</v>
+        <v>1.1683</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6905</v>
+        <v>0.1529</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5769</v>
+        <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4809</v>
+        <v>1.2591</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6019</v>
+        <v>0.9151</v>
       </c>
       <c r="U4" t="n">
-        <v>0.121</v>
+        <v>0.344</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0178</v>
+        <v>1.0813</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.0813</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>A. MONTENEGRO MOYA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8563</v>
+        <v>3.1622</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2039</v>
+        <v>1.2303</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6523</v>
+        <v>1.9319</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3593</v>
+        <v>2.7327</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7126</v>
+        <v>1.9139</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0719</v>
+        <v>0.8188</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4938</v>
+        <v>1.033</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3375</v>
+        <v>1.0291</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8437</v>
+        <v>0.0039</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8531</v>
+        <v>1.6998</v>
       </c>
       <c r="N5" t="n">
-        <v>0.625</v>
+        <v>0.8848</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2281</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>5.8934</v>
+        <v>0.033</v>
       </c>
       <c r="T5" t="n">
-        <v>4.464</v>
+        <v>0.1974</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4294</v>
+        <v>-0.1644</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>R. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5026</v>
+        <v>2.3184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4254</v>
+        <v>1.5535</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0773</v>
+        <v>0.7649</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2917</v>
+        <v>1.356</v>
       </c>
       <c r="H6" t="n">
-        <v>1.51</v>
+        <v>0.6481</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2183</v>
+        <v>0.7079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8479</v>
+        <v>0.6673</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6872</v>
+        <v>0.1009</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1607</v>
+        <v>0.5664</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4438</v>
+        <v>0.6888</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8228</v>
+        <v>0.5472</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.379</v>
+        <v>0.1415</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3787</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>4.3825</v>
+        <v>0.1606</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5331</v>
+        <v>0.2827</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8494</v>
+        <v>-0.1221</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MONTENEGRO MOYA</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4563</v>
+        <v>2.1105</v>
       </c>
       <c r="E7" t="n">
-        <v>0.721</v>
+        <v>-1.0963</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7353</v>
+        <v>3.2068</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7327</v>
+        <v>1.2917</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9139</v>
+        <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8188</v>
+        <v>-0.2183</v>
       </c>
       <c r="J7" t="n">
-        <v>1.033</v>
+        <v>0.8479</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0291</v>
+        <v>0.6872</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0039</v>
+        <v>0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6998</v>
+        <v>0.4438</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8848</v>
+        <v>0.8228</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.379</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.1627</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6729000000000001</v>
+        <v>1.9904</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.312</v>
+        <v>1.0115</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3609</v>
+        <v>0.979</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CALDERON QUINONES</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8204</v>
+        <v>1.6324</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0836</v>
+        <v>-0.0372</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7368</v>
+        <v>1.6696</v>
       </c>
       <c r="G8" t="n">
-        <v>1.356</v>
+        <v>1.3593</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6481</v>
+        <v>-0.7126</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7079</v>
+        <v>2.0719</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6673</v>
+        <v>-0.4938</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1009</v>
+        <v>-1.3375</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5664</v>
+        <v>0.8437</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6888</v>
+        <v>1.8531</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5472</v>
+        <v>0.625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1415</v>
+        <v>1.2281</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3374</v>
+        <v>2.6696</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1872</v>
+        <v>2.2229</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1502</v>
+        <v>0.4467</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6036</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. PAÑOS HUERTAS</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6027</v>
+        <v>0.6931</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6027</v>
+        <v>-2.8876</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3.5807</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6027</v>
+        <v>-1.3439</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.2751</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6027</v>
+        <v>-2.6191</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6027</v>
+        <v>-2.3197</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.9956</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6027</v>
+        <v>-3.3153</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.9757</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.6962</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.6891</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.6214</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.0677</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3479</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4097</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0605</v>
+        <v>0.2643</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3492</v>
+        <v>0.3773</v>
       </c>
       <c r="G10" t="n">
         <v>0.5379</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3264</v>
+        <v>-0.0945</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.2037</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3264</v>
+        <v>-0.2983</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>L. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3688</v>
+        <v>0.6027</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3804</v>
+        <v>0.6027</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7492</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3439</v>
+        <v>0.6027</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2751</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6191</v>
+        <v>0.6027</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3197</v>
+        <v>0.6027</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9956</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.3153</v>
+        <v>0.6027</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9757</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6962</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3648</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1286</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2362</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3479</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.3479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2413</v>
+        <v>-0.0675</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8096</v>
+        <v>-0.8885</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5683</v>
+        <v>0.821</v>
       </c>
       <c r="G12" t="n">
         <v>0.781</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4843</v>
+        <v>0.658</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0683</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5841</v>
+        <v>-0.3314</v>
       </c>
       <c r="V12" t="n">
         <v>0.674</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7403</v>
+        <v>-0.3793</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8675</v>
+        <v>-3.9278</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1273</v>
+        <v>3.5485</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3097</v>
@@ -1468,13 +1468,13 @@
         <v>2.5769</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2918</v>
+        <v>1.0691</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0772</v>
+        <v>1.017</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.369</v>
+        <v>0.0521</v>
       </c>
       <c r="V13" t="n">
         <v>0.2666</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.3906</v>
+        <v>-3.4184</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.5047</v>
+        <v>-1.7853</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8859</v>
+        <v>-1.6332</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7417</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2169</v>
+        <v>0.7552</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.121</v>
+        <v>0.5985</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0959</v>
+        <v>0.1568</v>
       </c>
       <c r="V14" t="n">
         <v>-3.6213</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>36.4816</v>
+        <v>38.04169999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>8.108799999999999</v>
+        <v>9.668799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>28.37289999999999</v>
+        <v>28.373</v>
       </c>
       <c r="G15" t="n">
         <v>21.5005</v>
@@ -1597,7 +1597,7 @@
         <v>8.035499999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>10.0159</v>
+        <v>10.01589999999999</v>
       </c>
       <c r="K15" t="n">
         <v>6.226</v>
@@ -1609,7 +1609,7 @@
         <v>11.4847</v>
       </c>
       <c r="N15" t="n">
-        <v>7.238899999999998</v>
+        <v>7.238899999999999</v>
       </c>
       <c r="O15" t="n">
         <v>4.2458</v>
@@ -1624,16 +1624,16 @@
         <v>17.84</v>
       </c>
       <c r="S15" t="n">
-        <v>9.800899999999999</v>
+        <v>11.3608</v>
       </c>
       <c r="T15" t="n">
-        <v>7.820300000000001</v>
+        <v>9.3804</v>
       </c>
       <c r="U15" t="n">
         <v>1.9805</v>
       </c>
       <c r="V15" t="n">
-        <v>5.180600000000002</v>
+        <v>5.1806</v>
       </c>
       <c r="W15" t="n">
         <v>8.1129</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7542</v>
+        <v>-0.7823</v>
       </c>
       <c r="E16" t="n">
         <v>-0.7819</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0277</v>
+        <v>-0.0004</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7355</v>
@@ -1702,13 +1702,13 @@
         <v>0.1982</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2169</v>
+        <v>-0.245</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1027</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1142</v>
+        <v>-0.1423</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6251</v>
+        <v>-1.0663</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2023</v>
+        <v>-1.2107</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4228</v>
+        <v>0.1444</v>
       </c>
       <c r="G17" t="n">
-        <v>1.309</v>
+        <v>1.322</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1255</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1835</v>
+        <v>1.3948</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9985</v>
+        <v>1.6792</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6324</v>
+        <v>0.5788</v>
       </c>
       <c r="L17" t="n">
-        <v>1.366</v>
+        <v>1.1004</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6895</v>
+        <v>-0.3572</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4931</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1825</v>
+        <v>0.2945</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2513</v>
+        <v>-1.1049</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4554</v>
+        <v>-0.3485</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7067</v>
+        <v>-0.7564</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8811</v>
+        <v>1.6899</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.674</v>
+        <v>2.4142</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2071</v>
+        <v>-0.7243000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9097</v>
+        <v>-1.52</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1574</v>
+        <v>-0.8136</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2477</v>
+        <v>-0.7065</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9755</v>
+        <v>1.309</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7555</v>
+        <v>1.1255</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2201</v>
+        <v>0.1835</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9367</v>
+        <v>1.9985</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2977</v>
+        <v>0.6324</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.639</v>
+        <v>1.366</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0388</v>
+        <v>-0.6895</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4577</v>
+        <v>0.4931</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4189</v>
+        <v>-1.1825</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>0.06759999999999999</v>
+        <v>-1.1462</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4444</v>
+        <v>-0.1558</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3767</v>
+        <v>-0.9903</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7947</v>
+        <v>-1.8811</v>
       </c>
       <c r="W18" t="n">
         <v>-0.674</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1207</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2417</v>
+        <v>-2.5104</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0257</v>
+        <v>-3.8705</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.216</v>
+        <v>1.36</v>
       </c>
       <c r="G19" t="n">
-        <v>1.322</v>
+        <v>-1.9755</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-1.7555</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3948</v>
+        <v>-0.2201</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6792</v>
+        <v>-1.9367</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5788</v>
+        <v>-1.2977</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1004</v>
+        <v>-0.639</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3572</v>
+        <v>-0.0388</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.4577</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2945</v>
+        <v>0.4189</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9733</v>
+        <v>0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.9556</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2803</v>
+        <v>-0.5331</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1635</v>
+        <v>-0.2687</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1168</v>
+        <v>-0.2644</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6899</v>
+        <v>-0.7947</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4142</v>
+        <v>-0.674</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3985</v>
+        <v>-2.594</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4133</v>
+        <v>-1.904</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9851</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3799</v>
@@ -2014,13 +2014,13 @@
         <v>2.7751</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0168</v>
+        <v>-1.2123</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7963</v>
+        <v>-0.287</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2204</v>
+        <v>-0.9253</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7947</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4336</v>
+        <v>-3.6406</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1117</v>
+        <v>-3.0098</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.322</v>
+        <v>-0.6308</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8889</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2169</v>
+        <v>-0.4239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3485</v>
+        <v>-0.2467</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1316</v>
+        <v>-0.1773</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3278</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2765</v>
+        <v>-4.17</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7852</v>
+        <v>-3.0908</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4912</v>
+        <v>-1.0792</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8063</v>
@@ -2170,13 +2170,13 @@
         <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2719</v>
+        <v>-1.1655</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1724</v>
+        <v>-0.478</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0995</v>
+        <v>-0.6875</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. IBADIN SANCHEZ</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7199</v>
+        <v>-6.0078</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5433</v>
+        <v>-4.6254</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1766</v>
+        <v>-1.3824</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.8492</v>
+        <v>-5.573</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.2038</v>
+        <v>-0.4764</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6455</v>
+        <v>-5.0966</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2661</v>
+        <v>-4.5459</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6673</v>
+        <v>-0.6319</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5988</v>
+        <v>-3.9141</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5832</v>
+        <v>-1.0271</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5365</v>
+        <v>0.1554</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0467</v>
+        <v>-1.1825</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.276</v>
+        <v>-0.8975</v>
       </c>
       <c r="T23" t="n">
-        <v>0.705</v>
+        <v>-0.3706</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.981</v>
+        <v>-0.5269</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.4627</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.2734</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>E. IBADIN SANCHEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.542</v>
+        <v>-6.0138</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0328</v>
+        <v>-4.0527</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5091</v>
+        <v>-1.9611</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.573</v>
+        <v>-4.8492</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4764</v>
+        <v>-3.2038</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.0966</v>
+        <v>-1.6455</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.5459</v>
+        <v>-2.2661</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6319</v>
+        <v>-1.6673</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.9141</v>
+        <v>-0.5988</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0271</v>
+        <v>-2.5832</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1554</v>
+        <v>-1.5365</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1825</v>
+        <v>-1.0467</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4317</v>
+        <v>-0.5698</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7781</v>
+        <v>0.1956</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6536</v>
+        <v>-0.7655</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4627</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2734</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5805</v>
+        <v>-6.1391</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3192</v>
+        <v>-5.0136</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2613</v>
+        <v>-1.1255</v>
       </c>
       <c r="G25" t="n">
         <v>-4.923</v>
@@ -2404,13 +2404,13 @@
         <v>1.784</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9067</v>
+        <v>-0.4652</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2237</v>
+        <v>0.0819</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6829</v>
+        <v>-0.5471</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5349</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-36.4817</v>
+        <v>-34.4443</v>
       </c>
       <c r="E26" t="n">
-        <v>-28.37280000000001</v>
+        <v>-28.373</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.108700000000001</v>
+        <v>-6.071499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-21.5003</v>
@@ -2452,7 +2452,7 @@
         <v>-13.4649</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.035599999999999</v>
+        <v>-8.035600000000001</v>
       </c>
       <c r="J26" t="n">
         <v>-11.4845</v>
@@ -2470,10 +2470,10 @@
         <v>-6.226100000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.789600000000001</v>
+        <v>-3.7896</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.8399</v>
@@ -2482,13 +2482,13 @@
         <v>17.84</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.8009</v>
+        <v>-7.763399999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.9804</v>
+        <v>-1.9805</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.8202</v>
+        <v>-5.783</v>
       </c>
       <c r="V26" t="n">
         <v>-5.1806</v>
